--- a/legal_forms/003_limited_liability_company_agreement_form--legal_forms.xlsx
+++ b/legal_forms/003_limited_liability_company_agreement_form--legal_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="47" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -551,14 +551,10 @@
           <t>Owner Address</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Enter address of owner</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -581,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -601,14 +597,10 @@
           <t>Manager Address</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Enter address of manager</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -628,14 +620,10 @@
           <t>Capital Structure</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Enter the number of capital structure members</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -647,22 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>distribution_purpose</t>
+          <t>number_of_members</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Distribution of Purpose</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Enter distribution purpose of llc</t>
-        </is>
-      </c>
+          <t>Number of Members</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -674,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>profit_allocation</t>
+          <t>capital_currency</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Profit Allocation</t>
+          <t>Capital Currency</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -697,22 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>operating_agreement</t>
+          <t>manager_percentage</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Operating Agreement</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Enter operating agreement of llc</t>
-        </is>
-      </c>
+          <t>Manager Percentage</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -735,7 +715,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -747,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>manager_details</t>
+          <t>operating_agreement</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Manager Details</t>
+          <t>Operating Agreement</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -770,22 +750,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>manager_address</t>
+          <t>manager_details_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Manager Address</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Enter address of manager</t>
-        </is>
-      </c>
+          <t>Manager Details 2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -797,22 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>number_of_members</t>
+          <t>manager_address_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Number of Members</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Enter number of members</t>
-        </is>
-      </c>
+          <t>Manager Address 2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -832,14 +804,10 @@
           <t>Capital Amount</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Enter capital amount of llc</t>
-        </is>
-      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -851,22 +819,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>capital_currency</t>
+          <t>distribution_purpose</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Capital Currency</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Enter currency of capital</t>
-        </is>
-      </c>
+          <t>Distribution of Purpose</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -878,292 +842,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>manager_percentage</t>
+          <t>operating_agreement_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Manager Percentage</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Enter manager percentage</t>
-        </is>
-      </c>
+          <t>Operating Agreement 2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>distribution_purpose</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Distribution of Purpose</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Enter distribution purpose of llc</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>operating_agreement</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Operating Agreement</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Enter operating agreement of llc</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>operating_agreement</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Operating Agreement</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Enter operating agreement of llc</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>operating_agreement</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Operating Agreement</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Enter operating agreement of llc</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>operating_agreement</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Operating Agreement</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Enter operating agreement of llc</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>operating_agreement</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Operating Agreement</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Enter operating agreement of llc</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>operating_agreement</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Operating Agreement</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Enter operating agreement of llc</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>operating_agreement</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Operating Agreement</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Enter operating agreement of llc</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>operating_agreement</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Operating Agreement</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Enter operating agreement of llc</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>operating_agreement</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Operating Agreement</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Enter operating agreement of llc</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1178,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1211,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'member_management',_'value':_'member_management'}</t>
+          <t>member_management</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Member Management', 'value': 'member_management'}</t>
+          <t>Member Management</t>
         </is>
       </c>
     </row>
@@ -1228,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'managerial_management',_'value':_'managerial_management'}</t>
+          <t>managerial_management</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Managerial Management', 'value': 'managerial_management'}</t>
+          <t>Managerial Management</t>
         </is>
       </c>
     </row>
@@ -1245,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'hybrid_management',_'value':_'hybrid_management'}</t>
+          <t>hybrid_management</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Hybrid Management', 'value': 'hybrid_management'}</t>
+          <t>Hybrid Management</t>
         </is>
       </c>
     </row>
@@ -1262,29 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'no_management',_'value':_'no_management'}</t>
+          <t>no_management</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'No Management', 'value': 'no_management'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>management_structure_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>{'id':_5,_'label':_'other_(specify_below)',_'value':_'other'}</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>{'id': 5, 'label': 'Other (Specify below)', 'value': 'other'}</t>
+          <t>No Management</t>
         </is>
       </c>
     </row>
